--- a/SubRES_TMPL/SubRES_TRA_NewVehicles.xlsx
+++ b/SubRES_TMPL/SubRES_TRA_NewVehicles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9789AD9-7D3C-487B-9BB0-5BCECAD6E2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DB867A-3B71-470A-99F5-9E94C8798621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="8" r:id="rId1"/>
@@ -272,7 +272,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="412">
   <si>
     <t>~FI_T</t>
   </si>
@@ -1586,6 +1586,9 @@
   <si>
     <t>RCAP_BND~0</t>
   </si>
+  <si>
+    <t>FI_T</t>
+  </si>
 </sst>
 </file>
 
@@ -1599,7 +1602,7 @@
     <numFmt numFmtId="168" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2961,21 +2964,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3AADF5-6ADD-4D31-A7A7-24B8240AB9AE}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="21.7265625" style="81" customWidth="1"/>
-    <col min="5" max="6" width="14.1796875" style="81" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" style="81" customWidth="1"/>
-    <col min="8" max="10" width="8.1796875" style="81" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" style="81" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" style="81" customWidth="1"/>
+    <col min="1" max="4" width="21.7109375" style="81" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" style="81" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="81" customWidth="1"/>
+    <col min="8" max="10" width="8.140625" style="81" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="81" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" style="81" customWidth="1"/>
     <col min="13" max="13" width="10" style="81" customWidth="1"/>
-    <col min="14" max="14" width="11.453125" style="81" customWidth="1"/>
-    <col min="15" max="15" width="13.453125" style="81" customWidth="1"/>
-    <col min="16" max="16384" width="8.81640625" style="81"/>
+    <col min="14" max="14" width="11.42578125" style="81" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="81" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="79"/>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -3003,7 +3006,7 @@
       <c r="Y1" s="80"/>
       <c r="Z1" s="80"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
       <c r="C2" s="79"/>
@@ -3031,7 +3034,7 @@
       <c r="Y2" s="80"/>
       <c r="Z2" s="80"/>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="79"/>
       <c r="B3" s="79"/>
       <c r="C3" s="79"/>
@@ -3059,7 +3062,7 @@
       <c r="Y3" s="80"/>
       <c r="Z3" s="80"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="79"/>
       <c r="B4" s="79"/>
       <c r="C4" s="79"/>
@@ -3087,7 +3090,7 @@
       <c r="Y4" s="80"/>
       <c r="Z4" s="80"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="79"/>
       <c r="B5" s="79"/>
       <c r="C5" s="79"/>
@@ -3115,7 +3118,7 @@
       <c r="Y5" s="80"/>
       <c r="Z5" s="80"/>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="79"/>
       <c r="B6" s="79"/>
       <c r="C6" s="79"/>
@@ -3143,7 +3146,7 @@
       <c r="Y6" s="80"/>
       <c r="Z6" s="80"/>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="79"/>
       <c r="B7" s="79"/>
       <c r="C7" s="79"/>
@@ -3171,7 +3174,7 @@
       <c r="Y7" s="80"/>
       <c r="Z7" s="80"/>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="79"/>
       <c r="B8" s="79"/>
       <c r="C8" s="79"/>
@@ -3199,7 +3202,7 @@
       <c r="Y8" s="80"/>
       <c r="Z8" s="80"/>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="79"/>
       <c r="B9" s="79"/>
       <c r="C9" s="79"/>
@@ -3227,7 +3230,7 @@
       <c r="Y9" s="80"/>
       <c r="Z9" s="80"/>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="79"/>
       <c r="B10" s="79"/>
       <c r="C10" s="79"/>
@@ -3255,7 +3258,7 @@
       <c r="Y10" s="80"/>
       <c r="Z10" s="80"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="79"/>
       <c r="B11" s="79"/>
       <c r="C11" s="79"/>
@@ -3283,7 +3286,7 @@
       <c r="Y11" s="80"/>
       <c r="Z11" s="80"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="79"/>
       <c r="B12" s="79"/>
       <c r="C12" s="79"/>
@@ -3311,7 +3314,7 @@
       <c r="Y12" s="80"/>
       <c r="Z12" s="80"/>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="79"/>
       <c r="B13" s="79"/>
       <c r="C13" s="79"/>
@@ -3339,7 +3342,7 @@
       <c r="Y13" s="80"/>
       <c r="Z13" s="80"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="79"/>
       <c r="B14" s="79"/>
       <c r="C14" s="79"/>
@@ -3367,7 +3370,7 @@
       <c r="Y14" s="80"/>
       <c r="Z14" s="80"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="79"/>
       <c r="B15" s="79"/>
       <c r="C15" s="79"/>
@@ -3395,7 +3398,7 @@
       <c r="Y15" s="80"/>
       <c r="Z15" s="80"/>
     </row>
-    <row r="16" spans="1:26" ht="102.75" customHeight="1">
+    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="100" t="s">
         <v>389</v>
       </c>
@@ -3425,7 +3428,7 @@
       <c r="Y16" s="80"/>
       <c r="Z16" s="80"/>
     </row>
-    <row r="17" spans="1:26" ht="17.25" customHeight="1">
+    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="84"/>
       <c r="B17" s="84"/>
       <c r="C17" s="84"/>
@@ -3453,7 +3456,7 @@
       <c r="Y17" s="80"/>
       <c r="Z17" s="80"/>
     </row>
-    <row r="18" spans="1:26" ht="17.25" customHeight="1">
+    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="84"/>
       <c r="B18" s="84"/>
       <c r="C18" s="84"/>
@@ -3481,7 +3484,7 @@
       <c r="Y18" s="80"/>
       <c r="Z18" s="80"/>
     </row>
-    <row r="19" spans="1:26" ht="17.25" customHeight="1">
+    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="87" t="s">
         <v>390</v>
       </c>
@@ -3513,7 +3516,7 @@
       <c r="Y19" s="80"/>
       <c r="Z19" s="80"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" customHeight="1">
+    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="87" t="s">
         <v>391</v>
       </c>
@@ -3545,7 +3548,7 @@
       <c r="Y20" s="80"/>
       <c r="Z20" s="80"/>
     </row>
-    <row r="21" spans="1:26" ht="17.25" customHeight="1">
+    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="87" t="s">
         <v>392</v>
       </c>
@@ -3577,7 +3580,7 @@
       <c r="Y21" s="80"/>
       <c r="Z21" s="80"/>
     </row>
-    <row r="22" spans="1:26" ht="17.25" customHeight="1">
+    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="87"/>
       <c r="B22" s="90"/>
       <c r="C22" s="90"/>
@@ -3605,7 +3608,7 @@
       <c r="Y22" s="80"/>
       <c r="Z22" s="80"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" customHeight="1">
+    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="87" t="s">
         <v>393</v>
       </c>
@@ -3637,7 +3640,7 @@
       <c r="Y23" s="80"/>
       <c r="Z23" s="80"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="87"/>
       <c r="B24" s="90"/>
       <c r="C24" s="90"/>
@@ -3665,7 +3668,7 @@
       <c r="Y24" s="80"/>
       <c r="Z24" s="80"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1">
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="87"/>
       <c r="B25" s="90"/>
       <c r="C25" s="90"/>
@@ -3693,7 +3696,7 @@
       <c r="Y25" s="80"/>
       <c r="Z25" s="80"/>
     </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1">
+    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="87" t="s">
         <v>394</v>
       </c>
@@ -3725,7 +3728,7 @@
       <c r="Y26" s="80"/>
       <c r="Z26" s="80"/>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="87"/>
       <c r="B27" s="99"/>
       <c r="C27" s="99"/>
@@ -3753,7 +3756,7 @@
       <c r="Y27" s="80"/>
       <c r="Z27" s="80"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="87"/>
       <c r="B28" s="90"/>
       <c r="C28" s="90"/>
@@ -3781,7 +3784,7 @@
       <c r="Y28" s="80"/>
       <c r="Z28" s="80"/>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="87" t="s">
         <v>395</v>
       </c>
@@ -3813,7 +3816,7 @@
       <c r="Y29" s="80"/>
       <c r="Z29" s="80"/>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="87" t="s">
         <v>396</v>
       </c>
@@ -3845,7 +3848,7 @@
       <c r="Y30" s="80"/>
       <c r="Z30" s="80"/>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="87" t="s">
         <v>398</v>
       </c>
@@ -3877,7 +3880,7 @@
       <c r="Y31" s="80"/>
       <c r="Z31" s="80"/>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="93"/>
       <c r="B32" s="94" t="s">
         <v>400</v>
@@ -3907,7 +3910,7 @@
       <c r="Y32" s="80"/>
       <c r="Z32" s="80"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="79"/>
       <c r="B33" s="79"/>
       <c r="C33" s="79"/>
@@ -3935,7 +3938,7 @@
       <c r="Y33" s="80"/>
       <c r="Z33" s="80"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="79"/>
       <c r="B34" s="79"/>
       <c r="C34" s="79"/>
@@ -3963,7 +3966,7 @@
       <c r="Y34" s="80"/>
       <c r="Z34" s="80"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="79"/>
       <c r="B35" s="79"/>
       <c r="C35" s="79"/>
@@ -3991,7 +3994,7 @@
       <c r="Y35" s="80"/>
       <c r="Z35" s="80"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="79"/>
       <c r="B36" s="79"/>
       <c r="C36" s="79"/>
@@ -4019,7 +4022,7 @@
       <c r="Y36" s="80"/>
       <c r="Z36" s="80"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="79"/>
       <c r="B37" s="79"/>
       <c r="C37" s="79"/>
@@ -4047,7 +4050,7 @@
       <c r="Y37" s="80"/>
       <c r="Z37" s="80"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="79"/>
       <c r="B38" s="79"/>
       <c r="C38" s="79"/>
@@ -4075,7 +4078,7 @@
       <c r="Y38" s="80"/>
       <c r="Z38" s="80"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="79"/>
       <c r="B39" s="79"/>
       <c r="C39" s="79"/>
@@ -4103,7 +4106,7 @@
       <c r="Y39" s="80"/>
       <c r="Z39" s="80"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="79"/>
       <c r="B40" s="79"/>
       <c r="C40" s="79"/>
@@ -4131,7 +4134,7 @@
       <c r="Y40" s="80"/>
       <c r="Z40" s="80"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="79"/>
       <c r="B41" s="79"/>
       <c r="C41" s="79"/>
@@ -4159,7 +4162,7 @@
       <c r="Y41" s="80"/>
       <c r="Z41" s="80"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="79"/>
       <c r="B42" s="79"/>
       <c r="C42" s="79"/>
@@ -4187,7 +4190,7 @@
       <c r="Y42" s="80"/>
       <c r="Z42" s="80"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="80"/>
       <c r="B43" s="80"/>
       <c r="C43" s="80"/>
@@ -4215,7 +4218,7 @@
       <c r="Y43" s="80"/>
       <c r="Z43" s="80"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="80"/>
       <c r="B44" s="80"/>
       <c r="C44" s="80"/>
@@ -4243,7 +4246,7 @@
       <c r="Y44" s="80"/>
       <c r="Z44" s="80"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="80"/>
       <c r="B45" s="80"/>
       <c r="C45" s="80"/>
@@ -4271,7 +4274,7 @@
       <c r="Y45" s="80"/>
       <c r="Z45" s="80"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="80"/>
       <c r="B46" s="80"/>
       <c r="C46" s="80"/>
@@ -4299,7 +4302,7 @@
       <c r="Y46" s="80"/>
       <c r="Z46" s="80"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="80"/>
       <c r="B47" s="80"/>
       <c r="C47" s="80"/>
@@ -4327,7 +4330,7 @@
       <c r="Y47" s="80"/>
       <c r="Z47" s="80"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="80"/>
       <c r="B48" s="80"/>
       <c r="C48" s="80"/>
@@ -4355,7 +4358,7 @@
       <c r="Y48" s="80"/>
       <c r="Z48" s="80"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="80"/>
       <c r="B49" s="80"/>
       <c r="C49" s="80"/>
@@ -4383,7 +4386,7 @@
       <c r="Y49" s="80"/>
       <c r="Z49" s="80"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="80"/>
       <c r="B50" s="80"/>
       <c r="C50" s="80"/>
@@ -4411,7 +4414,7 @@
       <c r="Y50" s="80"/>
       <c r="Z50" s="80"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="80"/>
       <c r="B51" s="80"/>
       <c r="C51" s="80"/>
@@ -4439,7 +4442,7 @@
       <c r="Y51" s="80"/>
       <c r="Z51" s="80"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="80"/>
       <c r="B52" s="80"/>
       <c r="C52" s="80"/>
@@ -4467,7 +4470,7 @@
       <c r="Y52" s="80"/>
       <c r="Z52" s="80"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="80"/>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
@@ -4495,7 +4498,7 @@
       <c r="Y53" s="80"/>
       <c r="Z53" s="80"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="80"/>
       <c r="B54" s="80"/>
       <c r="C54" s="80"/>
@@ -4523,7 +4526,7 @@
       <c r="Y54" s="80"/>
       <c r="Z54" s="80"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="80"/>
       <c r="B55" s="80"/>
       <c r="C55" s="80"/>
@@ -4551,7 +4554,7 @@
       <c r="Y55" s="80"/>
       <c r="Z55" s="80"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="80"/>
       <c r="B56" s="80"/>
       <c r="C56" s="80"/>
@@ -4579,7 +4582,7 @@
       <c r="Y56" s="80"/>
       <c r="Z56" s="80"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="80"/>
       <c r="B57" s="80"/>
       <c r="C57" s="80"/>
@@ -4607,7 +4610,7 @@
       <c r="Y57" s="80"/>
       <c r="Z57" s="80"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="80"/>
       <c r="B58" s="80"/>
       <c r="C58" s="80"/>
@@ -4635,7 +4638,7 @@
       <c r="Y58" s="80"/>
       <c r="Z58" s="80"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="80"/>
       <c r="B59" s="80"/>
       <c r="C59" s="80"/>
@@ -4663,7 +4666,7 @@
       <c r="Y59" s="80"/>
       <c r="Z59" s="80"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="80"/>
       <c r="B60" s="80"/>
       <c r="C60" s="80"/>
@@ -4691,7 +4694,7 @@
       <c r="Y60" s="80"/>
       <c r="Z60" s="80"/>
     </row>
-    <row r="61" spans="1:26">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="80"/>
       <c r="B61" s="80"/>
       <c r="C61" s="80"/>
@@ -4719,7 +4722,7 @@
       <c r="Y61" s="80"/>
       <c r="Z61" s="80"/>
     </row>
-    <row r="62" spans="1:26">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="80"/>
       <c r="B62" s="80"/>
       <c r="C62" s="80"/>
@@ -4747,7 +4750,7 @@
       <c r="Y62" s="80"/>
       <c r="Z62" s="80"/>
     </row>
-    <row r="63" spans="1:26">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="80"/>
       <c r="B63" s="80"/>
       <c r="C63" s="80"/>
@@ -4775,7 +4778,7 @@
       <c r="Y63" s="80"/>
       <c r="Z63" s="80"/>
     </row>
-    <row r="64" spans="1:26">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="80"/>
       <c r="B64" s="80"/>
       <c r="C64" s="80"/>
@@ -4803,7 +4806,7 @@
       <c r="Y64" s="80"/>
       <c r="Z64" s="80"/>
     </row>
-    <row r="65" spans="1:26">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="80"/>
       <c r="B65" s="80"/>
       <c r="C65" s="80"/>
@@ -4831,7 +4834,7 @@
       <c r="Y65" s="80"/>
       <c r="Z65" s="80"/>
     </row>
-    <row r="66" spans="1:26">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="80"/>
       <c r="B66" s="80"/>
       <c r="C66" s="80"/>
@@ -4859,7 +4862,7 @@
       <c r="Y66" s="80"/>
       <c r="Z66" s="80"/>
     </row>
-    <row r="67" spans="1:26">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="80"/>
       <c r="B67" s="80"/>
       <c r="C67" s="80"/>
@@ -4887,7 +4890,7 @@
       <c r="Y67" s="80"/>
       <c r="Z67" s="80"/>
     </row>
-    <row r="68" spans="1:26">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="80"/>
       <c r="B68" s="80"/>
       <c r="C68" s="80"/>
@@ -4915,7 +4918,7 @@
       <c r="Y68" s="80"/>
       <c r="Z68" s="80"/>
     </row>
-    <row r="69" spans="1:26">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="80"/>
       <c r="B69" s="80"/>
       <c r="C69" s="80"/>
@@ -4943,7 +4946,7 @@
       <c r="Y69" s="80"/>
       <c r="Z69" s="80"/>
     </row>
-    <row r="70" spans="1:26">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="80"/>
       <c r="B70" s="80"/>
       <c r="C70" s="80"/>
@@ -4971,7 +4974,7 @@
       <c r="Y70" s="80"/>
       <c r="Z70" s="80"/>
     </row>
-    <row r="71" spans="1:26">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="80"/>
       <c r="B71" s="80"/>
       <c r="C71" s="80"/>
@@ -4999,7 +5002,7 @@
       <c r="Y71" s="80"/>
       <c r="Z71" s="80"/>
     </row>
-    <row r="72" spans="1:26">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="80"/>
       <c r="B72" s="80"/>
       <c r="C72" s="80"/>
@@ -5027,7 +5030,7 @@
       <c r="Y72" s="80"/>
       <c r="Z72" s="80"/>
     </row>
-    <row r="73" spans="1:26">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="80"/>
       <c r="B73" s="80"/>
       <c r="C73" s="80"/>
@@ -5055,7 +5058,7 @@
       <c r="Y73" s="80"/>
       <c r="Z73" s="80"/>
     </row>
-    <row r="74" spans="1:26">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="80"/>
       <c r="B74" s="80"/>
       <c r="C74" s="80"/>
@@ -5083,7 +5086,7 @@
       <c r="Y74" s="80"/>
       <c r="Z74" s="80"/>
     </row>
-    <row r="75" spans="1:26">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="80"/>
       <c r="B75" s="80"/>
       <c r="C75" s="80"/>
@@ -5111,7 +5114,7 @@
       <c r="Y75" s="80"/>
       <c r="Z75" s="80"/>
     </row>
-    <row r="76" spans="1:26">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="80"/>
       <c r="B76" s="80"/>
       <c r="C76" s="80"/>
@@ -5139,7 +5142,7 @@
       <c r="Y76" s="80"/>
       <c r="Z76" s="80"/>
     </row>
-    <row r="77" spans="1:26">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="80"/>
       <c r="B77" s="80"/>
       <c r="C77" s="80"/>
@@ -5167,7 +5170,7 @@
       <c r="Y77" s="80"/>
       <c r="Z77" s="80"/>
     </row>
-    <row r="78" spans="1:26">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="80"/>
       <c r="B78" s="80"/>
       <c r="C78" s="80"/>
@@ -5195,7 +5198,7 @@
       <c r="Y78" s="80"/>
       <c r="Z78" s="80"/>
     </row>
-    <row r="79" spans="1:26">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="80"/>
       <c r="B79" s="80"/>
       <c r="C79" s="80"/>
@@ -5223,7 +5226,7 @@
       <c r="Y79" s="80"/>
       <c r="Z79" s="80"/>
     </row>
-    <row r="80" spans="1:26">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="80"/>
       <c r="B80" s="80"/>
       <c r="C80" s="80"/>
@@ -5251,7 +5254,7 @@
       <c r="Y80" s="80"/>
       <c r="Z80" s="80"/>
     </row>
-    <row r="81" spans="1:26">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="80"/>
       <c r="B81" s="80"/>
       <c r="C81" s="80"/>
@@ -5279,7 +5282,7 @@
       <c r="Y81" s="80"/>
       <c r="Z81" s="80"/>
     </row>
-    <row r="82" spans="1:26">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="80"/>
       <c r="B82" s="80"/>
       <c r="C82" s="80"/>
@@ -5307,7 +5310,7 @@
       <c r="Y82" s="80"/>
       <c r="Z82" s="80"/>
     </row>
-    <row r="83" spans="1:26">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="80"/>
       <c r="B83" s="80"/>
       <c r="C83" s="80"/>
@@ -5335,7 +5338,7 @@
       <c r="Y83" s="80"/>
       <c r="Z83" s="80"/>
     </row>
-    <row r="84" spans="1:26">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="80"/>
       <c r="B84" s="80"/>
       <c r="C84" s="80"/>
@@ -5363,7 +5366,7 @@
       <c r="Y84" s="80"/>
       <c r="Z84" s="80"/>
     </row>
-    <row r="85" spans="1:26">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="80"/>
       <c r="B85" s="80"/>
       <c r="C85" s="80"/>
@@ -5391,7 +5394,7 @@
       <c r="Y85" s="80"/>
       <c r="Z85" s="80"/>
     </row>
-    <row r="86" spans="1:26">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="80"/>
       <c r="B86" s="80"/>
       <c r="C86" s="80"/>
@@ -5419,7 +5422,7 @@
       <c r="Y86" s="80"/>
       <c r="Z86" s="80"/>
     </row>
-    <row r="87" spans="1:26">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="80"/>
       <c r="B87" s="80"/>
       <c r="C87" s="80"/>
@@ -5447,7 +5450,7 @@
       <c r="Y87" s="80"/>
       <c r="Z87" s="80"/>
     </row>
-    <row r="88" spans="1:26">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="80"/>
       <c r="B88" s="80"/>
       <c r="C88" s="80"/>
@@ -5475,7 +5478,7 @@
       <c r="Y88" s="80"/>
       <c r="Z88" s="80"/>
     </row>
-    <row r="89" spans="1:26">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="80"/>
       <c r="B89" s="80"/>
       <c r="C89" s="80"/>
@@ -5503,7 +5506,7 @@
       <c r="Y89" s="80"/>
       <c r="Z89" s="80"/>
     </row>
-    <row r="90" spans="1:26">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="80"/>
       <c r="B90" s="80"/>
       <c r="C90" s="80"/>
@@ -5531,7 +5534,7 @@
       <c r="Y90" s="80"/>
       <c r="Z90" s="80"/>
     </row>
-    <row r="91" spans="1:26">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="80"/>
       <c r="B91" s="80"/>
       <c r="C91" s="80"/>
@@ -5559,7 +5562,7 @@
       <c r="Y91" s="80"/>
       <c r="Z91" s="80"/>
     </row>
-    <row r="92" spans="1:26">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="80"/>
       <c r="B92" s="80"/>
       <c r="C92" s="80"/>
@@ -5587,7 +5590,7 @@
       <c r="Y92" s="80"/>
       <c r="Z92" s="80"/>
     </row>
-    <row r="93" spans="1:26">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="80"/>
       <c r="B93" s="80"/>
       <c r="C93" s="80"/>
@@ -5615,7 +5618,7 @@
       <c r="Y93" s="80"/>
       <c r="Z93" s="80"/>
     </row>
-    <row r="94" spans="1:26">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="80"/>
       <c r="B94" s="80"/>
       <c r="C94" s="80"/>
@@ -5643,7 +5646,7 @@
       <c r="Y94" s="80"/>
       <c r="Z94" s="80"/>
     </row>
-    <row r="95" spans="1:26">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="80"/>
       <c r="B95" s="80"/>
       <c r="C95" s="80"/>
@@ -5671,7 +5674,7 @@
       <c r="Y95" s="80"/>
       <c r="Z95" s="80"/>
     </row>
-    <row r="96" spans="1:26">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="80"/>
       <c r="B96" s="80"/>
       <c r="C96" s="80"/>
@@ -5699,7 +5702,7 @@
       <c r="Y96" s="80"/>
       <c r="Z96" s="80"/>
     </row>
-    <row r="97" spans="1:26">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="80"/>
       <c r="B97" s="80"/>
       <c r="C97" s="80"/>
@@ -5727,7 +5730,7 @@
       <c r="Y97" s="80"/>
       <c r="Z97" s="80"/>
     </row>
-    <row r="98" spans="1:26">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="80"/>
       <c r="B98" s="80"/>
       <c r="C98" s="80"/>
@@ -5755,7 +5758,7 @@
       <c r="Y98" s="80"/>
       <c r="Z98" s="80"/>
     </row>
-    <row r="99" spans="1:26">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="80"/>
       <c r="B99" s="80"/>
       <c r="C99" s="80"/>
@@ -5808,26 +5811,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="60.7265625" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
     <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="60.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.81640625" customWidth="1"/>
+    <col min="12" max="12" width="60.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="19"/>
     </row>
-    <row r="2" spans="1:8" ht="14.5">
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="20"/>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -5837,7 +5840,7 @@
       <c r="G2" s="21"/>
       <c r="H2" s="21"/>
     </row>
-    <row r="3" spans="1:8" ht="14.5">
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="20"/>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -5847,7 +5850,7 @@
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
     </row>
-    <row r="4" spans="1:8" ht="14.5">
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
         <v>41</v>
       </c>
@@ -5873,7 +5876,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="29">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>49</v>
       </c>
@@ -5899,7 +5902,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>58</v>
       </c>
@@ -5917,7 +5920,7 @@
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="21"/>
       <c r="B7" s="48" t="s">
         <v>61</v>
@@ -5933,7 +5936,7 @@
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" s="48" t="s">
         <v>62</v>
       </c>
@@ -5948,7 +5951,7 @@
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="21"/>
       <c r="B9" s="48" t="s">
         <v>63</v>
@@ -5964,7 +5967,7 @@
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
       <c r="B10" s="48" t="s">
         <v>65</v>
@@ -5980,7 +5983,7 @@
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="21"/>
       <c r="B11" s="48" t="s">
         <v>66</v>
@@ -5996,7 +5999,7 @@
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="21"/>
       <c r="B12" s="48" t="s">
         <v>380</v>
@@ -6012,7 +6015,7 @@
       <c r="G12" s="21"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="21"/>
       <c r="B13" s="48" t="s">
         <v>67</v>
@@ -6028,7 +6031,7 @@
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="21"/>
       <c r="B14" s="48" t="s">
         <v>69</v>
@@ -6044,7 +6047,7 @@
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="21"/>
       <c r="B15" s="48" t="s">
         <v>39</v>
@@ -6064,7 +6067,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="48" t="s">
         <v>120</v>
       </c>
@@ -6077,7 +6080,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B17" s="48" t="s">
         <v>388</v>
       </c>
@@ -6090,7 +6093,7 @@
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="28"/>
       <c r="B18" s="60" t="s">
         <v>72</v>
@@ -6106,7 +6109,7 @@
       <c r="G18" s="28"/>
       <c r="H18" s="28"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
         <v>73</v>
       </c>
@@ -6124,7 +6127,7 @@
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="21"/>
       <c r="B20" s="21" t="s">
         <v>189</v>
@@ -6141,7 +6144,7 @@
       <c r="H20" s="21"/>
       <c r="I20" s="21"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="21"/>
       <c r="B21" s="21" t="s">
         <v>191</v>
@@ -6158,7 +6161,7 @@
       <c r="H21" s="21"/>
       <c r="I21" s="21"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B22" s="21" t="s">
         <v>353</v>
       </c>
@@ -6174,7 +6177,7 @@
       <c r="H22" s="21"/>
       <c r="I22" s="21"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B23" s="21" t="s">
         <v>76</v>
       </c>
@@ -6189,7 +6192,7 @@
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>78</v>
       </c>
@@ -6204,7 +6207,7 @@
       <c r="G24" s="21"/>
       <c r="H24" s="21"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>80</v>
       </c>
@@ -6219,7 +6222,7 @@
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>82</v>
       </c>
@@ -6234,7 +6237,7 @@
       <c r="G26" s="21"/>
       <c r="H26" s="21"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="28"/>
       <c r="B27" s="28" t="s">
         <v>84</v>
@@ -6250,7 +6253,7 @@
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
     </row>
-    <row r="28" spans="1:9" ht="14.5">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>86</v>
       </c>
@@ -6268,7 +6271,7 @@
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
     </row>
-    <row r="29" spans="1:9" ht="14.5">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B29" s="29" t="s">
         <v>90</v>
       </c>
@@ -6283,7 +6286,7 @@
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
     </row>
-    <row r="30" spans="1:9" ht="14.5">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B30" s="29" t="s">
         <v>92</v>
       </c>
@@ -6298,7 +6301,7 @@
       <c r="G30" s="21"/>
       <c r="H30" s="21"/>
     </row>
-    <row r="31" spans="1:9" ht="14.5">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B31" s="29" t="s">
         <v>94</v>
       </c>
@@ -6313,7 +6316,7 @@
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B32" s="21" t="s">
         <v>96</v>
       </c>
@@ -6328,7 +6331,7 @@
       <c r="G32" s="21"/>
       <c r="H32" s="21"/>
     </row>
-    <row r="33" spans="1:9" ht="13" thickBot="1">
+    <row r="33" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="30"/>
       <c r="B33" s="31" t="s">
         <v>98</v>
@@ -6344,7 +6347,7 @@
       <c r="G33" s="31"/>
       <c r="H33" s="31"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -6353,7 +6356,7 @@
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
       <c r="E35" s="21"/>
@@ -6361,13 +6364,13 @@
       <c r="G35" s="21"/>
       <c r="H35" s="21"/>
     </row>
-    <row r="38" spans="1:9" ht="21">
+    <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="B38" s="102" t="s">
         <v>100</v>
       </c>
       <c r="C38" s="102"/>
     </row>
-    <row r="39" spans="1:9" ht="15" thickBot="1">
+    <row r="39" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B39" s="25" t="s">
         <v>56</v>
       </c>
@@ -6375,19 +6378,19 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="13.5" thickBot="1">
+    <row r="40" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B40" s="49" t="s">
         <v>208</v>
       </c>
       <c r="C40" s="50"/>
     </row>
-    <row r="41" spans="1:9" ht="13">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B41" s="51" t="s">
         <v>209</v>
       </c>
       <c r="C41" s="51"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B42" s="52" t="s">
         <v>210</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B43" s="52" t="s">
         <v>212</v>
       </c>
@@ -6403,13 +6406,13 @@
         <v>213</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="13">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B44" s="51" t="s">
         <v>68</v>
       </c>
       <c r="C44" s="51"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B45" s="52" t="s">
         <v>214</v>
       </c>
@@ -6418,7 +6421,7 @@
       </c>
       <c r="I45" s="21"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B46" s="52" t="s">
         <v>216</v>
       </c>
@@ -6427,7 +6430,7 @@
       </c>
       <c r="I46" s="21"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B47" s="52" t="s">
         <v>218</v>
       </c>
@@ -6435,7 +6438,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B48" s="52" t="s">
         <v>220</v>
       </c>
@@ -6443,7 +6446,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="49" spans="2:3">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="52" t="s">
         <v>222</v>
       </c>
@@ -6451,7 +6454,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="2:3">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="52" t="s">
         <v>224</v>
       </c>
@@ -6459,7 +6462,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="51" spans="2:3">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="52" t="s">
         <v>226</v>
       </c>
@@ -6467,7 +6470,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="52" spans="2:3">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="52" t="s">
         <v>228</v>
       </c>
@@ -6475,7 +6478,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="2:3">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="52" t="s">
         <v>230</v>
       </c>
@@ -6483,7 +6486,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="54" spans="2:3">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="52" t="s">
         <v>232</v>
       </c>
@@ -6491,7 +6494,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="55" spans="2:3">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="52" t="s">
         <v>234</v>
       </c>
@@ -6499,7 +6502,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="2:3">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="52" t="s">
         <v>236</v>
       </c>
@@ -6507,7 +6510,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="57" spans="2:3">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="52" t="s">
         <v>238</v>
       </c>
@@ -6515,7 +6518,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="58" spans="2:3">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="52" t="s">
         <v>240</v>
       </c>
@@ -6523,7 +6526,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="59" spans="2:3">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="52" t="s">
         <v>242</v>
       </c>
@@ -6531,7 +6534,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" spans="2:3">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="52" t="s">
         <v>355</v>
       </c>
@@ -6539,7 +6542,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="61" spans="2:3">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="52" t="s">
         <v>356</v>
       </c>
@@ -6547,7 +6550,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="62" spans="2:3">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="52" t="s">
         <v>246</v>
       </c>
@@ -6555,7 +6558,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="63" spans="2:3">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" s="52" t="s">
         <v>248</v>
       </c>
@@ -6563,13 +6566,13 @@
         <v>249</v>
       </c>
     </row>
-    <row r="64" spans="2:3" ht="13">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="51" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="51"/>
     </row>
-    <row r="65" spans="2:3">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" s="52" t="s">
         <v>251</v>
       </c>
@@ -6577,7 +6580,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="66" spans="2:3">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" s="52" t="s">
         <v>327</v>
       </c>
@@ -6585,7 +6588,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="67" spans="2:3">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B67" s="52" t="s">
         <v>313</v>
       </c>
@@ -6593,7 +6596,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="2:3">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B68" s="52" t="s">
         <v>314</v>
       </c>
@@ -6601,7 +6604,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B69" s="52" t="s">
         <v>315</v>
       </c>
@@ -6609,7 +6612,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70" s="52" t="s">
         <v>316</v>
       </c>
@@ -6617,7 +6620,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B71" s="52" t="s">
         <v>317</v>
       </c>
@@ -6625,7 +6628,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B72" s="52" t="s">
         <v>318</v>
       </c>
@@ -6633,7 +6636,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73" s="52" t="s">
         <v>319</v>
       </c>
@@ -6641,7 +6644,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="52" t="s">
         <v>320</v>
       </c>
@@ -6649,7 +6652,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B75" s="52" t="s">
         <v>321</v>
       </c>
@@ -6657,7 +6660,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76" s="52" t="s">
         <v>322</v>
       </c>
@@ -6665,7 +6668,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77" s="52" t="s">
         <v>323</v>
       </c>
@@ -6673,7 +6676,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78" s="52" t="s">
         <v>324</v>
       </c>
@@ -6681,7 +6684,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" s="52" t="s">
         <v>357</v>
       </c>
@@ -6689,7 +6692,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B80" s="52" t="s">
         <v>358</v>
       </c>
@@ -6697,7 +6700,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="81" spans="2:3">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81" s="52" t="s">
         <v>359</v>
       </c>
@@ -6705,7 +6708,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="82" spans="2:3">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82" s="52" t="s">
         <v>325</v>
       </c>
@@ -6713,7 +6716,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="83" spans="2:3">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B83" s="52" t="s">
         <v>326</v>
       </c>
@@ -6721,13 +6724,13 @@
         <v>270</v>
       </c>
     </row>
-    <row r="84" spans="2:3" ht="13">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B84" s="51" t="s">
         <v>271</v>
       </c>
       <c r="C84" s="51"/>
     </row>
-    <row r="85" spans="2:3">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85" s="52" t="s">
         <v>272</v>
       </c>
@@ -6735,7 +6738,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="86" spans="2:3">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86" s="52" t="s">
         <v>274</v>
       </c>
@@ -6743,7 +6746,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="87" spans="2:3">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87" s="52" t="s">
         <v>276</v>
       </c>
@@ -6751,7 +6754,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="88" spans="2:3">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B88" s="52" t="s">
         <v>278</v>
       </c>
@@ -6759,7 +6762,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="89" spans="2:3">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B89" s="52" t="s">
         <v>280</v>
       </c>
@@ -6767,13 +6770,13 @@
         <v>281</v>
       </c>
     </row>
-    <row r="90" spans="2:3" ht="13">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B90" s="51" t="s">
         <v>282</v>
       </c>
       <c r="C90" s="51"/>
     </row>
-    <row r="91" spans="2:3">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B91" s="52" t="s">
         <v>360</v>
       </c>
@@ -6781,7 +6784,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="92" spans="2:3">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92" s="52" t="s">
         <v>361</v>
       </c>
@@ -6789,7 +6792,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="2:3">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93" s="52" t="s">
         <v>285</v>
       </c>
@@ -6797,19 +6800,19 @@
         <v>286</v>
       </c>
     </row>
-    <row r="94" spans="2:3" ht="13">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94" s="53" t="s">
         <v>75</v>
       </c>
       <c r="C94" s="54"/>
     </row>
-    <row r="95" spans="2:3" ht="13">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95" s="51" t="s">
         <v>287</v>
       </c>
       <c r="C95" s="51"/>
     </row>
-    <row r="96" spans="2:3">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="52" t="s">
         <v>288</v>
       </c>
@@ -6817,7 +6820,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="97" spans="2:10">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B97" s="52" t="s">
         <v>290</v>
       </c>
@@ -6825,7 +6828,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="98" spans="2:10">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B98" s="52" t="s">
         <v>292</v>
       </c>
@@ -6833,7 +6836,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="99" spans="2:10">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B99" s="52" t="s">
         <v>382</v>
       </c>
@@ -6841,7 +6844,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="100" spans="2:10">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B100" s="52" t="s">
         <v>295</v>
       </c>
@@ -6849,7 +6852,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="101" spans="2:10">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B101" s="52" t="s">
         <v>297</v>
       </c>
@@ -6857,7 +6860,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="102" spans="2:10">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B102" s="52" t="s">
         <v>299</v>
       </c>
@@ -6865,13 +6868,13 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="2:10" ht="13">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B103" s="51" t="s">
         <v>329</v>
       </c>
       <c r="C103" s="51"/>
     </row>
-    <row r="104" spans="2:10">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B104" s="52" t="s">
         <v>346</v>
       </c>
@@ -6879,7 +6882,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="2:10">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B105" s="52" t="s">
         <v>347</v>
       </c>
@@ -6888,7 +6891,7 @@
       </c>
       <c r="J105" s="21"/>
     </row>
-    <row r="106" spans="2:10">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B106" s="52" t="s">
         <v>348</v>
       </c>
@@ -6897,7 +6900,7 @@
       </c>
       <c r="J106" s="21"/>
     </row>
-    <row r="107" spans="2:10">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B107" s="52" t="s">
         <v>349</v>
       </c>
@@ -6906,7 +6909,7 @@
       </c>
       <c r="J107" s="21"/>
     </row>
-    <row r="108" spans="2:10">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B108" s="52" t="s">
         <v>350</v>
       </c>
@@ -6915,7 +6918,7 @@
       </c>
       <c r="J108" s="21"/>
     </row>
-    <row r="109" spans="2:10">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B109" s="52" t="s">
         <v>351</v>
       </c>
@@ -6924,7 +6927,7 @@
       </c>
       <c r="J109" s="21"/>
     </row>
-    <row r="110" spans="2:10">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B110" s="52" t="s">
         <v>352</v>
       </c>
@@ -6933,14 +6936,14 @@
       </c>
       <c r="J110" s="21"/>
     </row>
-    <row r="111" spans="2:10" ht="13">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B111" s="51" t="s">
         <v>301</v>
       </c>
       <c r="C111" s="51"/>
       <c r="J111" s="21"/>
     </row>
-    <row r="112" spans="2:10">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B112" s="52" t="s">
         <v>334</v>
       </c>
@@ -6949,7 +6952,7 @@
       </c>
       <c r="J112" s="21"/>
     </row>
-    <row r="113" spans="2:10">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B113" s="52" t="s">
         <v>335</v>
       </c>
@@ -6958,7 +6961,7 @@
       </c>
       <c r="J113" s="21"/>
     </row>
-    <row r="114" spans="2:10">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B114" s="52" t="s">
         <v>336</v>
       </c>
@@ -6967,7 +6970,7 @@
       </c>
       <c r="J114" s="21"/>
     </row>
-    <row r="115" spans="2:10">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B115" s="52" t="s">
         <v>337</v>
       </c>
@@ -6976,7 +6979,7 @@
       </c>
       <c r="J115" s="21"/>
     </row>
-    <row r="116" spans="2:10">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B116" s="52" t="s">
         <v>338</v>
       </c>
@@ -6985,7 +6988,7 @@
       </c>
       <c r="J116" s="21"/>
     </row>
-    <row r="117" spans="2:10">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B117" s="52" t="s">
         <v>339</v>
       </c>
@@ -6994,7 +6997,7 @@
       </c>
       <c r="J117" s="21"/>
     </row>
-    <row r="118" spans="2:10">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B118" s="52" t="s">
         <v>340</v>
       </c>
@@ -7003,14 +7006,14 @@
       </c>
       <c r="J118" s="21"/>
     </row>
-    <row r="119" spans="2:10" ht="13">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B119" s="51" t="s">
         <v>309</v>
       </c>
       <c r="C119" s="51"/>
       <c r="J119" s="21"/>
     </row>
-    <row r="120" spans="2:10">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B120" s="52" t="s">
         <v>341</v>
       </c>
@@ -7018,7 +7021,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="121" spans="2:10">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B121" s="52" t="s">
         <v>362</v>
       </c>
@@ -7026,7 +7029,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="122" spans="2:10">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B122" s="52" t="s">
         <v>342</v>
       </c>
@@ -7034,19 +7037,19 @@
         <v>312</v>
       </c>
     </row>
-    <row r="123" spans="2:10" ht="13">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B123" s="53" t="s">
         <v>364</v>
       </c>
       <c r="C123" s="54"/>
     </row>
-    <row r="124" spans="2:10" ht="13">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B124" s="51" t="s">
         <v>368</v>
       </c>
       <c r="C124" s="51"/>
     </row>
-    <row r="125" spans="2:10">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B125" s="52" t="s">
         <v>377</v>
       </c>
@@ -7054,7 +7057,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="126" spans="2:10">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B126" s="52" t="s">
         <v>375</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="127" spans="2:10">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B127" s="52" t="s">
         <v>376</v>
       </c>
@@ -7070,13 +7073,13 @@
         <v>367</v>
       </c>
     </row>
-    <row r="128" spans="2:10" ht="13">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B128" s="51" t="s">
         <v>371</v>
       </c>
       <c r="C128" s="51"/>
     </row>
-    <row r="129" spans="2:3">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B129" t="s">
         <v>378</v>
       </c>
@@ -7084,7 +7087,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="2:3">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B130" s="28" t="s">
         <v>379</v>
       </c>
@@ -7105,31 +7108,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B3:Y298"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.26953125" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" customWidth="1"/>
-    <col min="3" max="3" width="49.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.54296875" customWidth="1"/>
-    <col min="6" max="8" width="13.453125" customWidth="1"/>
-    <col min="9" max="11" width="18.1796875" customWidth="1"/>
-    <col min="12" max="14" width="19.81640625" customWidth="1"/>
-    <col min="16" max="16" width="16.26953125" customWidth="1"/>
-    <col min="17" max="17" width="12.26953125" customWidth="1"/>
-    <col min="18" max="18" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="49.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" customWidth="1"/>
+    <col min="6" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="14" width="19.85546875" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="14.1796875" customWidth="1"/>
-    <col min="21" max="21" width="14.54296875" customWidth="1"/>
-    <col min="22" max="22" width="18.26953125" customWidth="1"/>
-    <col min="24" max="24" width="11.81640625" customWidth="1"/>
-    <col min="25" max="25" width="10.81640625" customWidth="1"/>
-    <col min="34" max="34" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10.7265625" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" customWidth="1"/>
+    <col min="22" max="22" width="18.28515625" customWidth="1"/>
+    <col min="24" max="24" width="11.85546875" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" customWidth="1"/>
+    <col min="34" max="34" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" ht="13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -7142,7 +7145,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="2:13" ht="13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
@@ -7171,7 +7174,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:13" ht="29.15" customHeight="1" thickBot="1">
+    <row r="5" spans="2:13" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>24</v>
       </c>
@@ -7200,7 +7203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="15" customHeight="1">
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
         <v>112</v>
       </c>
@@ -7213,7 +7216,7 @@
       <c r="I6" s="26"/>
       <c r="J6" s="26"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
@@ -7236,7 +7239,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
@@ -7259,7 +7262,7 @@
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="2:13" ht="14.5">
+    <row r="9" spans="2:13" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
         <v>113</v>
       </c>
@@ -7272,7 +7275,7 @@
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
@@ -7292,7 +7295,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
@@ -7312,7 +7315,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="2:13" ht="13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
@@ -7333,7 +7336,7 @@
       <c r="I12" s="9"/>
       <c r="M12" s="13"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -7354,7 +7357,7 @@
       <c r="I13" s="9"/>
       <c r="M13" s="17"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
@@ -7375,7 +7378,7 @@
       <c r="I14" s="9"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
@@ -7395,7 +7398,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
@@ -7415,7 +7418,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
@@ -7435,7 +7438,7 @@
       </c>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
@@ -7455,7 +7458,7 @@
       </c>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
@@ -7475,7 +7478,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
@@ -7495,7 +7498,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
@@ -7515,7 +7518,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>28</v>
       </c>
@@ -7535,7 +7538,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
@@ -7555,7 +7558,7 @@
       </c>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
@@ -7575,7 +7578,7 @@
       </c>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>28</v>
       </c>
@@ -7595,7 +7598,7 @@
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>28</v>
       </c>
@@ -7615,7 +7618,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>28</v>
       </c>
@@ -7635,7 +7638,7 @@
       </c>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>28</v>
       </c>
@@ -7655,7 +7658,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="2:10" ht="14.5">
+    <row r="29" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B29" s="26" t="s">
         <v>114</v>
       </c>
@@ -7668,7 +7671,7 @@
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>28</v>
       </c>
@@ -7688,7 +7691,7 @@
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>28</v>
       </c>
@@ -7708,7 +7711,7 @@
       </c>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>28</v>
       </c>
@@ -7728,7 +7731,7 @@
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>28</v>
       </c>
@@ -7748,7 +7751,7 @@
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>28</v>
       </c>
@@ -7768,7 +7771,7 @@
       </c>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>28</v>
       </c>
@@ -7788,7 +7791,7 @@
       </c>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>28</v>
       </c>
@@ -7808,7 +7811,7 @@
       </c>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>28</v>
       </c>
@@ -7828,7 +7831,7 @@
       </c>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>28</v>
       </c>
@@ -7848,7 +7851,7 @@
       </c>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>28</v>
       </c>
@@ -7868,7 +7871,7 @@
       </c>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>28</v>
       </c>
@@ -7888,7 +7891,7 @@
       </c>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>28</v>
       </c>
@@ -7908,7 +7911,7 @@
       </c>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>28</v>
       </c>
@@ -7928,7 +7931,7 @@
       </c>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>28</v>
       </c>
@@ -7948,7 +7951,7 @@
       </c>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>28</v>
       </c>
@@ -7968,7 +7971,7 @@
       </c>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>28</v>
       </c>
@@ -7988,7 +7991,7 @@
       </c>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>28</v>
       </c>
@@ -8008,7 +8011,7 @@
       </c>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>28</v>
       </c>
@@ -8028,7 +8031,7 @@
       </c>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>28</v>
       </c>
@@ -8048,7 +8051,7 @@
       </c>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" spans="2:10" ht="14.5">
+    <row r="49" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B49" s="26" t="s">
         <v>115</v>
       </c>
@@ -8061,7 +8064,7 @@
       <c r="I49" s="26"/>
       <c r="J49" s="26"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>28</v>
       </c>
@@ -8081,7 +8084,7 @@
       </c>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>28</v>
       </c>
@@ -8101,7 +8104,7 @@
       </c>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>28</v>
       </c>
@@ -8121,7 +8124,7 @@
       </c>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>28</v>
       </c>
@@ -8141,7 +8144,7 @@
       </c>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>28</v>
       </c>
@@ -8161,7 +8164,7 @@
       </c>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" spans="2:10" ht="14.5">
+    <row r="55" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B55" s="26" t="s">
         <v>116</v>
       </c>
@@ -8174,7 +8177,7 @@
       <c r="I55" s="26"/>
       <c r="J55" s="26"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>28</v>
       </c>
@@ -8194,7 +8197,7 @@
       </c>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>28</v>
       </c>
@@ -8214,7 +8217,7 @@
       </c>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
         <v>28</v>
       </c>
@@ -8234,7 +8237,7 @@
       </c>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:10" ht="14.5">
+    <row r="59" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B59" s="26" t="s">
         <v>117</v>
       </c>
@@ -8247,7 +8250,7 @@
       <c r="I59" s="26"/>
       <c r="J59" s="26"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
         <v>28</v>
       </c>
@@ -8267,7 +8270,7 @@
       </c>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
         <v>28</v>
       </c>
@@ -8287,7 +8290,7 @@
       </c>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
         <v>28</v>
       </c>
@@ -8307,7 +8310,7 @@
       </c>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" spans="2:10">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>28</v>
       </c>
@@ -8327,7 +8330,7 @@
       </c>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" spans="2:10">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>28</v>
       </c>
@@ -8347,7 +8350,7 @@
       </c>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" spans="2:10">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
         <v>28</v>
       </c>
@@ -8367,7 +8370,7 @@
       </c>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="2:10">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
         <v>28</v>
       </c>
@@ -8387,7 +8390,7 @@
       </c>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="2:10" ht="14.5">
+    <row r="67" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B67" s="26" t="s">
         <v>328</v>
       </c>
@@ -8400,7 +8403,7 @@
       <c r="I67" s="26"/>
       <c r="J67" s="26"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
         <v>28</v>
       </c>
@@ -8420,7 +8423,7 @@
       </c>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="2:10">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
         <v>28</v>
       </c>
@@ -8440,7 +8443,7 @@
       </c>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:10">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>28</v>
       </c>
@@ -8460,7 +8463,7 @@
       </c>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" spans="2:10">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
         <v>28</v>
       </c>
@@ -8480,7 +8483,7 @@
       </c>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" spans="2:10">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
         <v>28</v>
       </c>
@@ -8500,7 +8503,7 @@
       </c>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" spans="2:10">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
         <v>28</v>
       </c>
@@ -8520,7 +8523,7 @@
       </c>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" spans="2:10">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
         <v>28</v>
       </c>
@@ -8540,7 +8543,7 @@
       </c>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" spans="2:10" ht="14.5">
+    <row r="75" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B75" s="26" t="s">
         <v>118</v>
       </c>
@@ -8553,7 +8556,7 @@
       <c r="I75" s="26"/>
       <c r="J75" s="26"/>
     </row>
-    <row r="76" spans="2:10">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
         <v>28</v>
       </c>
@@ -8573,7 +8576,7 @@
       </c>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="2:10">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
         <v>28</v>
       </c>
@@ -8593,7 +8596,7 @@
       </c>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="2:10">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
         <v>28</v>
       </c>
@@ -8613,7 +8616,7 @@
       </c>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" spans="2:10">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
         <v>28</v>
       </c>
@@ -8633,7 +8636,7 @@
       </c>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="2:10">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
         <v>28</v>
       </c>
@@ -8653,7 +8656,7 @@
       </c>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="2:16">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
         <v>28</v>
       </c>
@@ -8673,7 +8676,7 @@
       </c>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="2:16">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
         <v>28</v>
       </c>
@@ -8693,7 +8696,7 @@
       </c>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="2:16" ht="14.5">
+    <row r="83" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B83" s="26" t="s">
         <v>119</v>
       </c>
@@ -8706,7 +8709,7 @@
       <c r="I83" s="26"/>
       <c r="J83" s="26"/>
     </row>
-    <row r="84" spans="2:16">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
         <v>28</v>
       </c>
@@ -8726,7 +8729,7 @@
       </c>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" spans="2:16">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
         <v>28</v>
       </c>
@@ -8746,7 +8749,7 @@
       </c>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="2:16">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
         <v>28</v>
       </c>
@@ -8766,7 +8769,7 @@
       </c>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="2:16" ht="14.5">
+    <row r="87" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B87" s="26" t="s">
         <v>363</v>
       </c>
@@ -8780,7 +8783,7 @@
       <c r="J87" s="26"/>
       <c r="P87" s="21"/>
     </row>
-    <row r="88" spans="2:16">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B88" s="2" t="s">
         <v>28</v>
       </c>
@@ -8800,7 +8803,7 @@
       </c>
       <c r="P88" s="21"/>
     </row>
-    <row r="89" spans="2:16">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
         <v>28</v>
       </c>
@@ -8820,7 +8823,7 @@
       </c>
       <c r="P89" s="21"/>
     </row>
-    <row r="90" spans="2:16">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
         <v>28</v>
       </c>
@@ -8840,7 +8843,7 @@
       </c>
       <c r="P90" s="21"/>
     </row>
-    <row r="91" spans="2:16" ht="14.5">
+    <row r="91" spans="2:16" ht="15" x14ac:dyDescent="0.25">
       <c r="B91" s="26" t="s">
         <v>374</v>
       </c>
@@ -8854,7 +8857,7 @@
       <c r="J91" s="26"/>
       <c r="P91" s="21"/>
     </row>
-    <row r="92" spans="2:16">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B92" s="56" t="s">
         <v>28</v>
       </c>
@@ -8874,7 +8877,7 @@
       </c>
       <c r="P92" s="21"/>
     </row>
-    <row r="93" spans="2:16">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B93" s="58" t="s">
         <v>28</v>
       </c>
@@ -8899,16 +8902,16 @@
       <c r="K93" s="46"/>
       <c r="P93" s="21"/>
     </row>
-    <row r="94" spans="2:16">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.2">
       <c r="M94">
         <v>2</v>
       </c>
       <c r="P94" s="21"/>
     </row>
-    <row r="95" spans="2:16">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.2">
       <c r="P95" s="21"/>
     </row>
-    <row r="96" spans="2:16" ht="13">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.2">
       <c r="D96" s="6" t="s">
         <v>0</v>
       </c>
@@ -8917,7 +8920,7 @@
       <c r="J96" s="7"/>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="2:25" ht="13">
+    <row r="97" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B97" s="10" t="s">
         <v>1</v>
       </c>
@@ -8991,7 +8994,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="98" spans="2:25" ht="20.5">
+    <row r="98" spans="2:25" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B98" s="35" t="s">
         <v>31</v>
       </c>
@@ -9060,7 +9063,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="2:25" ht="26.5" thickBot="1">
+    <row r="99" spans="2:25" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B99" s="34" t="s">
         <v>35</v>
       </c>
@@ -9125,7 +9128,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="2:25" ht="14.5">
+    <row r="100" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B100" s="26" t="s">
         <v>112</v>
       </c>
@@ -9152,14 +9155,14 @@
       <c r="W100" s="26"/>
       <c r="X100" s="26"/>
     </row>
-    <row r="101" spans="2:25">
+    <row r="101" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B101" t="str">
         <f>D7</f>
         <v>T-MOT-ICE_GSL01</v>
       </c>
       <c r="C101" t="str">
-        <f>Commodities!B8&amp;","&amp;Commodities!B10</f>
-        <v>TRAGSL,TRAETH</v>
+        <f>Commodities!B8</f>
+        <v>TRAGSL</v>
       </c>
       <c r="D101" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20</f>
@@ -9230,7 +9233,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="102" spans="2:25">
+    <row r="102" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B102" t="str">
         <f>D8</f>
         <v>T-MOT-EV_ELC01</v>
@@ -9308,7 +9311,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="103" spans="2:25" ht="14.5">
+    <row r="103" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B103" s="26" t="s">
         <v>113</v>
       </c>
@@ -9335,14 +9338,14 @@
       <c r="W103" s="26"/>
       <c r="X103" s="26"/>
     </row>
-    <row r="104" spans="2:25">
+    <row r="104" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B104" t="str">
         <f t="shared" ref="B104:B122" si="2">D10</f>
         <v>T-CAR-ICE_GSL21</v>
       </c>
       <c r="C104" t="str">
-        <f>Commodities!B8&amp;","&amp;Commodities!B10</f>
-        <v>TRAGSL,TRAETH</v>
+        <f>Commodities!B8</f>
+        <v>TRAGSL</v>
       </c>
       <c r="D104" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -9416,14 +9419,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="105" spans="2:25">
+    <row r="105" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B105" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-ICE_DST21</v>
       </c>
       <c r="C105" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D105" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -9497,7 +9500,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="106" spans="2:25">
+    <row r="106" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B106" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-ICE_DF21</v>
@@ -9575,7 +9578,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="107" spans="2:25">
+    <row r="107" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B107" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-ICE_NGB21</v>
@@ -9653,7 +9656,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="108" spans="2:25">
+    <row r="108" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B108" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-ICE_E8521</v>
@@ -9731,7 +9734,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="109" spans="2:25">
+    <row r="109" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B109" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-ICE_B10021</v>
@@ -9809,14 +9812,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="110" spans="2:25">
+    <row r="110" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B110" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-HEV_GSL21</v>
       </c>
       <c r="C110" t="str">
-        <f>Commodities!B8&amp;","&amp;Commodities!B10</f>
-        <v>TRAGSL,TRAETH</v>
+        <f>Commodities!B8</f>
+        <v>TRAGSL</v>
       </c>
       <c r="D110" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -9887,14 +9890,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="111" spans="2:25">
+    <row r="111" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B111" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-HEV_DST21</v>
       </c>
       <c r="C111" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D111" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -9965,7 +9968,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="112" spans="2:25">
+    <row r="112" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B112" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-PHEV10_GSL21</v>
@@ -10043,7 +10046,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="113" spans="2:24">
+    <row r="113" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B113" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-PHEV20_GSL21</v>
@@ -10121,7 +10124,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="114" spans="2:24">
+    <row r="114" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B114" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-PHEV40_GSL21</v>
@@ -10199,7 +10202,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="115" spans="2:24">
+    <row r="115" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B115" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-PHEV10_DST21</v>
@@ -10277,7 +10280,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="116" spans="2:24">
+    <row r="116" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B116" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-PHEV20_DST21</v>
@@ -10355,7 +10358,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="117" spans="2:24">
+    <row r="117" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B117" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-PHEV40_DST21</v>
@@ -10433,7 +10436,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="118" spans="2:24">
+    <row r="118" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B118" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-BEV100_ELC21</v>
@@ -10511,7 +10514,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="119" spans="2:24">
+    <row r="119" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B119" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-BEV150_ELC21</v>
@@ -10589,7 +10592,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="120" spans="2:24">
+    <row r="120" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B120" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-BEV250_ELC21</v>
@@ -10667,7 +10670,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="121" spans="2:24">
+    <row r="121" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B121" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-ICE_HYD21</v>
@@ -10745,7 +10748,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="122" spans="2:24">
+    <row r="122" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B122" t="str">
         <f t="shared" si="2"/>
         <v>T-CAR-FCV_HYD21</v>
@@ -10823,7 +10826,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="123" spans="2:24" ht="14.5">
+    <row r="123" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B123" s="26" t="s">
         <v>114</v>
       </c>
@@ -10850,14 +10853,14 @@
       <c r="W123" s="26"/>
       <c r="X123" s="26"/>
     </row>
-    <row r="124" spans="2:24">
+    <row r="124" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B124" t="str">
         <f t="shared" ref="B124:B142" si="7">D30</f>
         <v>T-TAX-ICE_GSL31</v>
       </c>
       <c r="C124" t="str">
-        <f>Commodities!B8&amp;","&amp;Commodities!B10</f>
-        <v>TRAGSL,TRAETH</v>
+        <f>Commodities!B8</f>
+        <v>TRAGSL</v>
       </c>
       <c r="D124" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -10928,14 +10931,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="125" spans="2:24">
+    <row r="125" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B125" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-ICE_DST31</v>
       </c>
       <c r="C125" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D125" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -11007,7 +11010,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="126" spans="2:24">
+    <row r="126" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B126" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-ICE_DF31</v>
@@ -11086,7 +11089,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="127" spans="2:24">
+    <row r="127" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B127" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-ICE_NGB31</v>
@@ -11165,7 +11168,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="128" spans="2:24">
+    <row r="128" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B128" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-ICE_E8531</v>
@@ -11244,7 +11247,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="129" spans="2:24">
+    <row r="129" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B129" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-ICE_B10031</v>
@@ -11323,14 +11326,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="130" spans="2:24">
+    <row r="130" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B130" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-HEV_GSL31</v>
       </c>
       <c r="C130" t="str">
-        <f>Commodities!B8&amp;","&amp;Commodities!B10</f>
-        <v>TRAGSL,TRAETH</v>
+        <f>Commodities!B8</f>
+        <v>TRAGSL</v>
       </c>
       <c r="D130" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -11402,14 +11405,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="131" spans="2:24">
+    <row r="131" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B131" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-HEV_DST31</v>
       </c>
       <c r="C131" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D131" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -11481,7 +11484,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="132" spans="2:24">
+    <row r="132" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B132" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-PHEV10_GSL31</v>
@@ -11560,7 +11563,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="133" spans="2:24">
+    <row r="133" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B133" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-PHEV20_GSL31</v>
@@ -11639,7 +11642,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="134" spans="2:24">
+    <row r="134" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B134" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-PHEV40_GSL31</v>
@@ -11718,7 +11721,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="135" spans="2:24">
+    <row r="135" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B135" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-PHEV10_DST31</v>
@@ -11797,7 +11800,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="136" spans="2:24">
+    <row r="136" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B136" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-PHEV20_DST31</v>
@@ -11876,7 +11879,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="137" spans="2:24">
+    <row r="137" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B137" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-PHEV40_DST31</v>
@@ -11955,7 +11958,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="138" spans="2:24">
+    <row r="138" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B138" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-BEV100_ELC31</v>
@@ -12034,7 +12037,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="139" spans="2:24">
+    <row r="139" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B139" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-BEV150_ELC31</v>
@@ -12113,7 +12116,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="140" spans="2:24">
+    <row r="140" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B140" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-BEV250_ELC31</v>
@@ -12192,7 +12195,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="141" spans="2:24">
+    <row r="141" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B141" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-ICE_HYD31</v>
@@ -12271,7 +12274,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="142" spans="2:24">
+    <row r="142" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B142" t="str">
         <f t="shared" si="7"/>
         <v>T-TAX-FCV_HYD31</v>
@@ -12350,7 +12353,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="143" spans="2:24" ht="14.5">
+    <row r="143" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B143" s="26" t="s">
         <v>115</v>
       </c>
@@ -12377,14 +12380,14 @@
       <c r="W143" s="26"/>
       <c r="X143" s="26"/>
     </row>
-    <row r="144" spans="2:24">
+    <row r="144" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B144" t="str">
         <f>D50</f>
         <v>T-BUS-ICE_DST41</v>
       </c>
       <c r="C144" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D144" t="str">
         <f>Commodities!B19&amp;","&amp;Commodities!B20&amp;","&amp;Commodities!B21</f>
@@ -12455,7 +12458,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="145" spans="2:24">
+    <row r="145" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B145" t="str">
         <f>D51</f>
         <v>T-BUS-ICE_B10041</v>
@@ -12533,7 +12536,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="146" spans="2:24">
+    <row r="146" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B146" t="str">
         <f>D52</f>
         <v>T-BUS-ICE_NGB41</v>
@@ -12611,7 +12614,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="147" spans="2:24">
+    <row r="147" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B147" t="str">
         <f>D53</f>
         <v>T-BUS-BEV_ELC41</v>
@@ -12692,7 +12695,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="148" spans="2:24">
+    <row r="148" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B148" t="str">
         <f>D54</f>
         <v>T-BUS-FCV_HYD41</v>
@@ -12770,7 +12773,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="149" spans="2:24" ht="14.5">
+    <row r="149" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B149" s="26" t="s">
         <v>116</v>
       </c>
@@ -12797,7 +12800,7 @@
       <c r="W149" s="26"/>
       <c r="X149" s="26"/>
     </row>
-    <row r="150" spans="2:24">
+    <row r="150" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B150" t="str">
         <f>D56</f>
         <v>T-LPT-BEV_ELC51</v>
@@ -12875,7 +12878,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="151" spans="2:24">
+    <row r="151" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B151" t="str">
         <f>D57</f>
         <v>T-HPT-BEV_ELC51</v>
@@ -12953,14 +12956,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="152" spans="2:24">
+    <row r="152" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B152" t="str">
         <f>D58</f>
         <v>T-HPT-ICE_DST51</v>
       </c>
       <c r="C152" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D152" t="str">
         <f>Commodities!B21</f>
@@ -13031,7 +13034,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="153" spans="2:24" ht="14.5">
+    <row r="153" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B153" s="26" t="s">
         <v>117</v>
       </c>
@@ -13058,14 +13061,14 @@
       <c r="W153" s="26"/>
       <c r="X153" s="26"/>
     </row>
-    <row r="154" spans="2:24">
+    <row r="154" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B154" t="str">
         <f t="shared" ref="B154:B160" si="16">D60</f>
         <v>T-LGT-ICE_DST61</v>
       </c>
       <c r="C154" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D154" t="str">
         <f>Commodities!B22</f>
@@ -13136,14 +13139,14 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="155" spans="2:24">
+    <row r="155" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B155" t="str">
         <f t="shared" si="16"/>
         <v>T-LGT-HEV_DST61</v>
       </c>
       <c r="C155" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D155" t="str">
         <f>D154</f>
@@ -13214,7 +13217,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="156" spans="2:24">
+    <row r="156" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B156" t="str">
         <f t="shared" si="16"/>
         <v>T-LGT-PHEV_DST61</v>
@@ -13292,7 +13295,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="157" spans="2:24">
+    <row r="157" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B157" t="str">
         <f t="shared" si="16"/>
         <v>T-LGT-ICE_NGB61</v>
@@ -13370,7 +13373,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="158" spans="2:24">
+    <row r="158" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B158" t="str">
         <f t="shared" si="16"/>
         <v>T-LGT-PHEV_NGB61</v>
@@ -13448,7 +13451,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="159" spans="2:24">
+    <row r="159" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B159" t="str">
         <f t="shared" si="16"/>
         <v>T-LGT-FCV_HYD61</v>
@@ -13526,7 +13529,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="160" spans="2:24">
+    <row r="160" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B160" t="str">
         <f t="shared" si="16"/>
         <v>T-LGT-BEV_ELC61</v>
@@ -13607,7 +13610,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="161" spans="2:25" ht="14.5">
+    <row r="161" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B161" s="26" t="s">
         <v>328</v>
       </c>
@@ -13634,14 +13637,14 @@
       <c r="W161" s="26"/>
       <c r="X161" s="26"/>
     </row>
-    <row r="162" spans="2:25">
+    <row r="162" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B162" t="str">
         <f t="shared" ref="B162:B168" si="21">D68</f>
         <v>T-MGT-ICE_DST71</v>
       </c>
       <c r="C162" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D162" t="str">
         <f>Commodities!B22</f>
@@ -13723,14 +13726,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="2:25">
+    <row r="163" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B163" t="str">
         <f t="shared" si="21"/>
         <v>T-MGT-HEV_DST71</v>
       </c>
       <c r="C163" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D163" t="str">
         <f>D162</f>
@@ -13813,7 +13816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:25">
+    <row r="164" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B164" t="str">
         <f t="shared" si="21"/>
         <v>T-MGT-FCV_HYD71</v>
@@ -13902,7 +13905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="2:25">
+    <row r="165" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B165" t="str">
         <f t="shared" si="21"/>
         <v>T-MGT-ICE_NGB71</v>
@@ -13992,7 +13995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:25">
+    <row r="166" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B166" t="str">
         <f t="shared" si="21"/>
         <v>T-MGT-HEV_NGB71</v>
@@ -14082,7 +14085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="2:25">
+    <row r="167" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B167" t="str">
         <f t="shared" si="21"/>
         <v>T-MGT-ICE_LNG71</v>
@@ -14172,7 +14175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:25">
+    <row r="168" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B168" t="str">
         <f t="shared" si="21"/>
         <v>T-MGT-BEV_ELC71</v>
@@ -14262,7 +14265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:25" ht="14.5">
+    <row r="169" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B169" s="26" t="s">
         <v>118</v>
       </c>
@@ -14289,14 +14292,14 @@
       <c r="W169" s="26"/>
       <c r="X169" s="26"/>
     </row>
-    <row r="170" spans="2:25">
+    <row r="170" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B170" t="str">
         <f t="shared" ref="B170:B176" si="32">D76</f>
         <v>T-HGT-ICE_DST81</v>
       </c>
       <c r="C170" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D170" t="str">
         <f>Commodities!B22</f>
@@ -14370,14 +14373,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="2:25">
+    <row r="171" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B171" t="str">
         <f t="shared" si="32"/>
         <v>T-HGT-HEV_DST81</v>
       </c>
       <c r="C171" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D171" t="str">
         <f>D170</f>
@@ -14452,7 +14455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:25">
+    <row r="172" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B172" t="str">
         <f t="shared" si="32"/>
         <v>T-HGT-FCV_HYD81</v>
@@ -14534,7 +14537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="2:25">
+    <row r="173" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B173" t="str">
         <f t="shared" si="32"/>
         <v>T-HGT-ICE_NGB81</v>
@@ -14616,7 +14619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:25">
+    <row r="174" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B174" t="str">
         <f t="shared" si="32"/>
         <v>T-HGT-HEV_NGB81</v>
@@ -14698,7 +14701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="2:25">
+    <row r="175" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B175" t="str">
         <f t="shared" si="32"/>
         <v>T-HGT-ICE_LNG81</v>
@@ -14780,7 +14783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="2:25">
+    <row r="176" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B176" t="str">
         <f t="shared" si="32"/>
         <v>T-HGT-BEV_ELC81</v>
@@ -14862,7 +14865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="2:24" ht="14.5">
+    <row r="177" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B177" s="26" t="s">
         <v>119</v>
       </c>
@@ -14889,14 +14892,14 @@
       <c r="W177" s="26"/>
       <c r="X177" s="26"/>
     </row>
-    <row r="178" spans="2:24">
+    <row r="178" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B178" t="str">
         <f>D84</f>
         <v>T-GTR-ICE_DST91</v>
       </c>
       <c r="C178" t="str">
-        <f>Commodities!B9&amp;","&amp;Commodities!B11</f>
-        <v>TRADST,TRABDL</v>
+        <f>Commodities!B9</f>
+        <v>TRADST</v>
       </c>
       <c r="D178" t="str">
         <f>Commodities!B22</f>
@@ -14967,7 +14970,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="179" spans="2:24">
+    <row r="179" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B179" t="str">
         <f>D85</f>
         <v>T-GTR-BEV_ELC91</v>
@@ -15045,7 +15048,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="180" spans="2:24">
+    <row r="180" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B180" t="str">
         <f>D86</f>
         <v>T-GTR-FCV_HYD91</v>
@@ -15123,7 +15126,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="181" spans="2:24" ht="14.5">
+    <row r="181" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B181" s="26" t="s">
         <v>363</v>
       </c>
@@ -15150,7 +15153,7 @@
       <c r="W181" s="26"/>
       <c r="X181" s="26"/>
     </row>
-    <row r="182" spans="2:24">
+    <row r="182" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B182" t="str">
         <f>D88</f>
         <v>T-TUR_NEW</v>
@@ -15180,7 +15183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="2:24">
+    <row r="183" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B183" t="str">
         <f t="shared" ref="B183:B184" si="42">D89</f>
         <v>T-NAV_NEW</v>
@@ -15210,7 +15213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="2:24">
+    <row r="184" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B184" t="str">
         <f t="shared" si="42"/>
         <v>T-OTH_NEW</v>
@@ -15240,7 +15243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="2:24" ht="14.5">
+    <row r="185" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B185" s="26" t="s">
         <v>374</v>
       </c>
@@ -15267,7 +15270,7 @@
       <c r="W185" s="26"/>
       <c r="X185" s="26"/>
     </row>
-    <row r="186" spans="2:24">
+    <row r="186" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B186" t="str">
         <f>Commodities!B129</f>
         <v>T-AVI_DOM_NEW</v>
@@ -15297,7 +15300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="2:24">
+    <row r="187" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B187" s="28" t="str">
         <f>Commodities!B130</f>
         <v>T-AVI_INT_NEW</v>
@@ -15341,19 +15344,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="2:24">
+    <row r="190" spans="2:24" x14ac:dyDescent="0.2">
       <c r="R190" s="46"/>
     </row>
-    <row r="193" spans="2:9" ht="14.5">
+    <row r="193" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="D193" s="77" t="s">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="F193" s="76"/>
       <c r="G193" s="75"/>
       <c r="H193" s="75"/>
       <c r="I193" s="75"/>
     </row>
-    <row r="194" spans="2:9" ht="14.5">
+    <row r="194" spans="2:9" ht="15" x14ac:dyDescent="0.2">
       <c r="B194" s="23" t="s">
         <v>1</v>
       </c>
@@ -15376,7 +15379,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="195" spans="2:9">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B195" s="61" t="str">
         <f>B101</f>
         <v>T-MOT-ICE_GSL01</v>
@@ -15401,7 +15404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="2:9">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B196" s="64" t="str">
         <f>B195</f>
         <v>T-MOT-ICE_GSL01</v>
@@ -15426,7 +15429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="2:9">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B197" s="69" t="str">
         <f>B104</f>
         <v>T-CAR-ICE_GSL21</v>
@@ -15451,7 +15454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="2:9">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B198" s="69" t="str">
         <f>B197</f>
         <v>T-CAR-ICE_GSL21</v>
@@ -15476,7 +15479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="2:9">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B199" s="69" t="str">
         <f>B105</f>
         <v>T-CAR-ICE_DST21</v>
@@ -15501,7 +15504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="2:9">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B200" s="69" t="str">
         <f>B199</f>
         <v>T-CAR-ICE_DST21</v>
@@ -15526,7 +15529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="2:9">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B201" s="69" t="str">
         <f>B106</f>
         <v>T-CAR-ICE_DF21</v>
@@ -15551,7 +15554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="2:9">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B202" s="69" t="str">
         <f>B201</f>
         <v>T-CAR-ICE_DF21</v>
@@ -15576,7 +15579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="2:9">
+    <row r="203" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B203" s="69" t="str">
         <f>B107</f>
         <v>T-CAR-ICE_NGB21</v>
@@ -15601,7 +15604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="2:9">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B204" s="69" t="str">
         <f>B203</f>
         <v>T-CAR-ICE_NGB21</v>
@@ -15626,7 +15629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="2:9">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B205" s="69" t="str">
         <f>TRA!B108</f>
         <v>T-CAR-ICE_E8521</v>
@@ -15651,7 +15654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="2:9">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B206" s="69" t="str">
         <f>B205</f>
         <v>T-CAR-ICE_E8521</v>
@@ -15676,7 +15679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="2:9">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B207" s="69" t="str">
         <f>B110</f>
         <v>T-CAR-HEV_GSL21</v>
@@ -15701,7 +15704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="2:9" ht="15" customHeight="1">
+    <row r="208" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B208" s="69" t="str">
         <f>B207</f>
         <v>T-CAR-HEV_GSL21</v>
@@ -15726,7 +15729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="2:8">
+    <row r="209" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B209" s="69" t="str">
         <f>B111</f>
         <v>T-CAR-HEV_DST21</v>
@@ -15751,7 +15754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="2:8">
+    <row r="210" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B210" s="69" t="str">
         <f>B209</f>
         <v>T-CAR-HEV_DST21</v>
@@ -15776,7 +15779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="2:8">
+    <row r="211" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B211" s="69" t="str">
         <f>B112</f>
         <v>T-CAR-PHEV10_GSL21</v>
@@ -15801,7 +15804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212" spans="2:8">
+    <row r="212" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B212" s="69" t="str">
         <f>B211</f>
         <v>T-CAR-PHEV10_GSL21</v>
@@ -15826,7 +15829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="2:8">
+    <row r="213" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B213" s="69" t="str">
         <f>B113</f>
         <v>T-CAR-PHEV20_GSL21</v>
@@ -15851,7 +15854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="2:8">
+    <row r="214" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B214" s="69" t="str">
         <f>B213</f>
         <v>T-CAR-PHEV20_GSL21</v>
@@ -15876,7 +15879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="2:8">
+    <row r="215" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B215" s="69" t="str">
         <f>B114</f>
         <v>T-CAR-PHEV40_GSL21</v>
@@ -15901,7 +15904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="2:8">
+    <row r="216" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B216" s="69" t="str">
         <f>B215</f>
         <v>T-CAR-PHEV40_GSL21</v>
@@ -15926,7 +15929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="2:8">
+    <row r="217" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B217" s="69" t="str">
         <f>B115</f>
         <v>T-CAR-PHEV10_DST21</v>
@@ -15950,7 +15953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="2:8">
+    <row r="218" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B218" s="69" t="str">
         <f>B217</f>
         <v>T-CAR-PHEV10_DST21</v>
@@ -15974,7 +15977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="2:8">
+    <row r="219" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B219" s="69" t="str">
         <f>B116</f>
         <v>T-CAR-PHEV20_DST21</v>
@@ -15999,7 +16002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="2:8">
+    <row r="220" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B220" s="69" t="str">
         <f>B219</f>
         <v>T-CAR-PHEV20_DST21</v>
@@ -16024,7 +16027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="2:8">
+    <row r="221" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B221" s="69" t="str">
         <f>B117</f>
         <v>T-CAR-PHEV40_DST21</v>
@@ -16049,7 +16052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="2:8">
+    <row r="222" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B222" s="69" t="str">
         <f>B221</f>
         <v>T-CAR-PHEV40_DST21</v>
@@ -16074,7 +16077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="2:8">
+    <row r="223" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B223" s="64" t="str">
         <f>B124</f>
         <v>T-TAX-ICE_GSL31</v>
@@ -16104,7 +16107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="2:8">
+    <row r="224" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B224" s="64" t="str">
         <f>B223</f>
         <v>T-TAX-ICE_GSL31</v>
@@ -16134,7 +16137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="2:8">
+    <row r="225" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B225" s="64" t="str">
         <f>B125</f>
         <v>T-TAX-ICE_DST31</v>
@@ -16164,7 +16167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="2:8">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B226" s="64" t="str">
         <f>B225</f>
         <v>T-TAX-ICE_DST31</v>
@@ -16194,7 +16197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="2:8">
+    <row r="227" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B227" s="64" t="str">
         <f>B126</f>
         <v>T-TAX-ICE_DF31</v>
@@ -16224,7 +16227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="2:8">
+    <row r="228" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B228" s="64" t="str">
         <f>B227</f>
         <v>T-TAX-ICE_DF31</v>
@@ -16254,7 +16257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="2:8">
+    <row r="229" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B229" s="64" t="str">
         <f>B127</f>
         <v>T-TAX-ICE_NGB31</v>
@@ -16284,7 +16287,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="2:8">
+    <row r="230" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B230" s="64" t="str">
         <f>B229</f>
         <v>T-TAX-ICE_NGB31</v>
@@ -16314,7 +16317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="2:8">
+    <row r="231" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B231" s="64" t="str">
         <f>B128</f>
         <v>T-TAX-ICE_E8531</v>
@@ -16344,7 +16347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="2:8">
+    <row r="232" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B232" s="64" t="str">
         <f>B231</f>
         <v>T-TAX-ICE_E8531</v>
@@ -16374,7 +16377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="2:8">
+    <row r="233" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B233" s="64" t="str">
         <f>B130</f>
         <v>T-TAX-HEV_GSL31</v>
@@ -16404,7 +16407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="234" spans="2:8">
+    <row r="234" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B234" s="64" t="str">
         <f>B233</f>
         <v>T-TAX-HEV_GSL31</v>
@@ -16434,7 +16437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="2:8">
+    <row r="235" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B235" s="64" t="str">
         <f>B131</f>
         <v>T-TAX-HEV_DST31</v>
@@ -16464,7 +16467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="2:8">
+    <row r="236" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B236" s="64" t="str">
         <f>B235</f>
         <v>T-TAX-HEV_DST31</v>
@@ -16494,7 +16497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="2:8">
+    <row r="237" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B237" s="64" t="str">
         <f>B132</f>
         <v>T-TAX-PHEV10_GSL31</v>
@@ -16524,7 +16527,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="2:8">
+    <row r="238" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B238" s="64" t="str">
         <f>B237</f>
         <v>T-TAX-PHEV10_GSL31</v>
@@ -16554,7 +16557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="2:8">
+    <row r="239" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B239" s="64" t="str">
         <f>B133</f>
         <v>T-TAX-PHEV20_GSL31</v>
@@ -16584,7 +16587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="2:8">
+    <row r="240" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B240" s="64" t="str">
         <f>B239</f>
         <v>T-TAX-PHEV20_GSL31</v>
@@ -16614,7 +16617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="2:8">
+    <row r="241" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B241" s="64" t="str">
         <f>B134</f>
         <v>T-TAX-PHEV40_GSL31</v>
@@ -16644,7 +16647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="2:8">
+    <row r="242" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B242" s="64" t="str">
         <f>B241</f>
         <v>T-TAX-PHEV40_GSL31</v>
@@ -16674,7 +16677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="2:8">
+    <row r="243" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B243" s="64" t="str">
         <f>B135</f>
         <v>T-TAX-PHEV10_DST31</v>
@@ -16704,7 +16707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="2:8">
+    <row r="244" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B244" s="64" t="str">
         <f>B243</f>
         <v>T-TAX-PHEV10_DST31</v>
@@ -16734,7 +16737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="2:8">
+    <row r="245" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B245" s="64" t="str">
         <f>B136</f>
         <v>T-TAX-PHEV20_DST31</v>
@@ -16764,7 +16767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="246" spans="2:8">
+    <row r="246" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B246" s="64" t="str">
         <f>B245</f>
         <v>T-TAX-PHEV20_DST31</v>
@@ -16794,7 +16797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="2:8">
+    <row r="247" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B247" s="64" t="str">
         <f>B137</f>
         <v>T-TAX-PHEV40_DST31</v>
@@ -16824,7 +16827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="2:8">
+    <row r="248" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B248" s="64" t="str">
         <f>B247</f>
         <v>T-TAX-PHEV40_DST31</v>
@@ -16854,7 +16857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="2:8">
+    <row r="249" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B249" s="69" t="str">
         <f>B144</f>
         <v>T-BUS-ICE_DST41</v>
@@ -16880,7 +16883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="250" spans="2:8">
+    <row r="250" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B250" s="69" t="str">
         <f>B249</f>
         <v>T-BUS-ICE_DST41</v>
@@ -16906,7 +16909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="2:8">
+    <row r="251" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B251" s="69" t="str">
         <f>B146</f>
         <v>T-BUS-ICE_NGB41</v>
@@ -16933,7 +16936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="2:8">
+    <row r="252" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B252" s="69" t="str">
         <f>B251</f>
         <v>T-BUS-ICE_NGB41</v>
@@ -16961,7 +16964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="2:8">
+    <row r="253" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B253" s="64" t="str">
         <f>B152</f>
         <v>T-HPT-ICE_DST51</v>
@@ -16986,7 +16989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="2:8">
+    <row r="254" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B254" s="64" t="str">
         <f>B253</f>
         <v>T-HPT-ICE_DST51</v>
@@ -17011,7 +17014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="2:8">
+    <row r="255" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B255" s="69" t="str">
         <f>B154</f>
         <v>T-LGT-ICE_DST61</v>
@@ -17036,7 +17039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="2:8">
+    <row r="256" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B256" s="69" t="str">
         <f>B255</f>
         <v>T-LGT-ICE_DST61</v>
@@ -17061,7 +17064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="2:8">
+    <row r="257" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B257" s="69" t="str">
         <f>B155</f>
         <v>T-LGT-HEV_DST61</v>
@@ -17086,7 +17089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="2:8">
+    <row r="258" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B258" s="69" t="str">
         <f>B257</f>
         <v>T-LGT-HEV_DST61</v>
@@ -17111,7 +17114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="2:8">
+    <row r="259" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B259" s="69" t="str">
         <f>B156</f>
         <v>T-LGT-PHEV_DST61</v>
@@ -17136,7 +17139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="2:8">
+    <row r="260" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B260" s="69" t="str">
         <f>B259</f>
         <v>T-LGT-PHEV_DST61</v>
@@ -17161,7 +17164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="2:8">
+    <row r="261" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B261" s="69" t="str">
         <f>B157</f>
         <v>T-LGT-ICE_NGB61</v>
@@ -17186,7 +17189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="2:8">
+    <row r="262" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B262" s="69" t="str">
         <f>B261</f>
         <v>T-LGT-ICE_NGB61</v>
@@ -17211,7 +17214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="2:8">
+    <row r="263" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B263" s="69" t="str">
         <f>B158</f>
         <v>T-LGT-PHEV_NGB61</v>
@@ -17236,7 +17239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="2:8">
+    <row r="264" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B264" s="69" t="str">
         <f>B263</f>
         <v>T-LGT-PHEV_NGB61</v>
@@ -17261,7 +17264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="2:8">
+    <row r="265" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B265" s="64" t="str">
         <f>B162</f>
         <v>T-MGT-ICE_DST71</v>
@@ -17286,7 +17289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="2:8">
+    <row r="266" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B266" s="64" t="str">
         <f>B265</f>
         <v>T-MGT-ICE_DST71</v>
@@ -17311,7 +17314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="2:8">
+    <row r="267" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B267" s="64" t="str">
         <f>B163</f>
         <v>T-MGT-HEV_DST71</v>
@@ -17336,7 +17339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="2:8">
+    <row r="268" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B268" s="64" t="str">
         <f>B267</f>
         <v>T-MGT-HEV_DST71</v>
@@ -17361,7 +17364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="2:8">
+    <row r="269" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B269" s="64" t="str">
         <f>B165</f>
         <v>T-MGT-ICE_NGB71</v>
@@ -17386,7 +17389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="2:8">
+    <row r="270" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B270" s="64" t="str">
         <f>B269</f>
         <v>T-MGT-ICE_NGB71</v>
@@ -17411,7 +17414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="2:8">
+    <row r="271" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B271" s="64" t="str">
         <f>B166</f>
         <v>T-MGT-HEV_NGB71</v>
@@ -17436,7 +17439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="2:8">
+    <row r="272" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B272" s="64" t="str">
         <f>B271</f>
         <v>T-MGT-HEV_NGB71</v>
@@ -17461,7 +17464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="2:8">
+    <row r="273" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B273" s="69" t="str">
         <f>B170</f>
         <v>T-HGT-ICE_DST81</v>
@@ -17486,7 +17489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="2:8">
+    <row r="274" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B274" s="69" t="str">
         <f>B273</f>
         <v>T-HGT-ICE_DST81</v>
@@ -17511,7 +17514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="2:8">
+    <row r="275" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B275" s="69" t="str">
         <f>B171</f>
         <v>T-HGT-HEV_DST81</v>
@@ -17536,7 +17539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="2:8">
+    <row r="276" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B276" s="69" t="str">
         <f>B275</f>
         <v>T-HGT-HEV_DST81</v>
@@ -17561,7 +17564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="2:8">
+    <row r="277" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B277" s="69" t="str">
         <f>B173</f>
         <v>T-HGT-ICE_NGB81</v>
@@ -17586,7 +17589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="2:8">
+    <row r="278" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B278" s="69" t="str">
         <f>B277</f>
         <v>T-HGT-ICE_NGB81</v>
@@ -17611,7 +17614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="2:8">
+    <row r="279" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B279" s="69" t="str">
         <f>B174</f>
         <v>T-HGT-HEV_NGB81</v>
@@ -17636,7 +17639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="2:8">
+    <row r="280" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B280" s="69" t="str">
         <f>B279</f>
         <v>T-HGT-HEV_NGB81</v>
@@ -17661,7 +17664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="2:8">
+    <row r="281" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B281" s="64" t="str">
         <f>B178</f>
         <v>T-GTR-ICE_DST91</v>
@@ -17686,7 +17689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="2:8">
+    <row r="282" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B282" s="64" t="str">
         <f>B281</f>
         <v>T-GTR-ICE_DST91</v>
@@ -17711,7 +17714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="2:8">
+    <row r="283" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B283" s="69" t="str">
         <f>B182</f>
         <v>T-TUR_NEW</v>
@@ -17736,7 +17739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="2:8">
+    <row r="284" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B284" s="69" t="str">
         <f>B283</f>
         <v>T-TUR_NEW</v>
@@ -17761,7 +17764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="2:8">
+    <row r="285" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B285" s="69" t="str">
         <f>B182</f>
         <v>T-TUR_NEW</v>
@@ -17786,7 +17789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="2:8">
+    <row r="286" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B286" s="69" t="str">
         <f>B285</f>
         <v>T-TUR_NEW</v>
@@ -17811,7 +17814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="2:8">
+    <row r="287" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B287" s="64" t="str">
         <f>B183</f>
         <v>T-NAV_NEW</v>
@@ -17836,7 +17839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="2:8">
+    <row r="288" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B288" s="64" t="str">
         <f>B287</f>
         <v>T-NAV_NEW</v>
@@ -17861,7 +17864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="2:8">
+    <row r="289" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B289" s="69" t="str">
         <f>B184</f>
         <v>T-OTH_NEW</v>
@@ -17886,7 +17889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="2:8">
+    <row r="290" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B290" s="69" t="str">
         <f>B289</f>
         <v>T-OTH_NEW</v>
@@ -17911,7 +17914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="2:8">
+    <row r="291" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B291" s="69" t="str">
         <f t="shared" ref="B291:B294" si="49">B290</f>
         <v>T-OTH_NEW</v>
@@ -17936,7 +17939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="2:8">
+    <row r="292" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B292" s="69" t="str">
         <f t="shared" si="49"/>
         <v>T-OTH_NEW</v>
@@ -17961,7 +17964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="2:8">
+    <row r="293" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B293" s="69" t="str">
         <f t="shared" si="49"/>
         <v>T-OTH_NEW</v>
@@ -17986,7 +17989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="2:8">
+    <row r="294" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B294" s="69" t="str">
         <f t="shared" si="49"/>
         <v>T-OTH_NEW</v>
@@ -18011,7 +18014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="2:8">
+    <row r="295" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B295" s="64" t="str">
         <f>B186</f>
         <v>T-AVI_DOM_NEW</v>
@@ -18036,7 +18039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="2:8">
+    <row r="296" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B296" s="64" t="str">
         <f>B295</f>
         <v>T-AVI_DOM_NEW</v>
@@ -18061,7 +18064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="2:8">
+    <row r="297" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B297" s="64" t="str">
         <f>B187</f>
         <v>T-AVI_INT_NEW</v>
@@ -18086,7 +18089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="2:8">
+    <row r="298" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B298" s="68" t="str">
         <f>B297</f>
         <v>T-AVI_INT_NEW</v>
@@ -18126,19 +18129,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:L96"/>
-  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" customWidth="1"/>
-    <col min="3" max="11" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="11" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>122</v>
       </c>
@@ -18173,7 +18176,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>133</v>
       </c>
@@ -18208,7 +18211,7 @@
         <v>2574</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>134</v>
       </c>
@@ -18247,7 +18250,7 @@
         <v>4.044339163234481E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -18286,7 +18289,7 @@
         <v>7.0982279191462321E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -18325,7 +18328,7 @@
         <v>3.9667538813275338E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -18364,7 +18367,7 @@
         <v>3.4071494011901911E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -18403,7 +18406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>139</v>
       </c>
@@ -18442,7 +18445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>140</v>
       </c>
@@ -18481,7 +18484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>141</v>
       </c>
@@ -18520,7 +18523,7 @@
         <v>9.7889515257063141E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>142</v>
       </c>
@@ -18559,7 +18562,7 @@
         <v>2.81535528281486E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>143</v>
       </c>
@@ -18598,7 +18601,7 @@
         <v>5.7611198692605467E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -18637,7 +18640,7 @@
         <v>8.8694833975750467E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>145</v>
       </c>
@@ -18676,7 +18679,7 @@
         <v>1.0399729276888665E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>146</v>
       </c>
@@ -18715,7 +18718,7 @@
         <v>9.0378599668199111E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>147</v>
       </c>
@@ -18754,7 +18757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -18793,7 +18796,7 @@
         <v>4.9027295162475133E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -18832,7 +18835,7 @@
         <v>7.5934531228075966E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -18871,7 +18874,7 @@
         <v>5.7817542527464363E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -18910,7 +18913,7 @@
         <v>8.2620071477504387E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>152</v>
       </c>
@@ -18949,7 +18952,7 @@
         <v>3.8875178487417154E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>153</v>
       </c>
@@ -18988,7 +18991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>154</v>
       </c>
@@ -19027,7 +19030,7 @@
         <v>1.7844614838597853E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>155</v>
       </c>
@@ -19066,7 +19069,7 @@
         <v>3.2627087167889597E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>156</v>
       </c>
@@ -19105,7 +19108,7 @@
         <v>4.7624157085434599E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>157</v>
       </c>
@@ -19144,7 +19147,7 @@
         <v>6.1160312652178582E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>158</v>
       </c>
@@ -19183,7 +19186,7 @@
         <v>7.6570070239441387E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>159</v>
       </c>
@@ -19222,7 +19225,7 @@
         <v>4.0385615358584315E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>160</v>
       </c>
@@ -19261,7 +19264,7 @@
         <v>4.4355670741269594E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>161</v>
       </c>
@@ -19300,7 +19303,7 @@
         <v>6.0252399778799404E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>162</v>
       </c>
@@ -19339,7 +19342,7 @@
         <v>5.8395305265069287E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>163</v>
       </c>
@@ -19378,7 +19381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>164</v>
       </c>
@@ -19417,7 +19420,7 @@
         <v>2.9713512219681899E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>165</v>
       </c>
@@ -19456,7 +19459,7 @@
         <v>7.1543534422278537E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -19495,7 +19498,7 @@
         <v>8.253753394356084E-6</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>167</v>
       </c>
@@ -19534,7 +19537,7 @@
         <v>6.1077775118235022E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -19573,7 +19576,7 @@
         <v>1.5434518847445876E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>169</v>
       </c>
@@ -19612,7 +19615,7 @@
         <v>1.0143862921663627E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>170</v>
       </c>
@@ -19651,7 +19654,7 @@
         <v>9.9045040732272994E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>171</v>
       </c>
@@ -19690,7 +19693,7 @@
         <v>9.4786103980785269E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>172</v>
       </c>
@@ -19729,7 +19732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>173</v>
       </c>
@@ -19768,7 +19771,7 @@
         <v>0.1113926558102297</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>174</v>
       </c>
@@ -19807,17 +19810,17 @@
         <v>1.3948843236461781E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="14.5">
+    <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>123</v>
       </c>
@@ -19849,7 +19852,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15.5">
+    <row r="52" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>144</v>
       </c>
@@ -19881,7 +19884,7 @@
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.5">
+    <row r="53" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>146</v>
       </c>
@@ -19913,7 +19916,7 @@
         <v>43995</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15.5">
+    <row r="54" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>150</v>
       </c>
@@ -19945,7 +19948,7 @@
         <v>41670</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15.5">
+    <row r="55" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>158</v>
       </c>
@@ -19977,7 +19980,7 @@
         <v>37720</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15.5">
+    <row r="56" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -20009,7 +20012,7 @@
         <v>37990</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15.5">
+    <row r="57" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -20041,7 +20044,7 @@
         <v>42025</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.5">
+    <row r="58" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -20073,7 +20076,7 @@
         <v>40395</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15.5">
+    <row r="59" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -20105,17 +20108,17 @@
         <v>73975</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="13">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="47" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>123</v>
       </c>
@@ -20147,7 +20150,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>144</v>
       </c>
@@ -20192,7 +20195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>146</v>
       </c>
@@ -20237,7 +20240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>150</v>
       </c>
@@ -20282,7 +20285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>158</v>
       </c>
@@ -20327,7 +20330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>162</v>
       </c>
@@ -20372,7 +20375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>165</v>
       </c>
@@ -20417,7 +20420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>171</v>
       </c>
@@ -20462,7 +20465,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>173</v>
       </c>
@@ -20507,7 +20510,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="14.5">
+    <row r="73" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="40" t="s">
         <v>177</v>
       </c>
@@ -20552,12 +20555,12 @@
         <v>931</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
         <v>123</v>
       </c>
@@ -20589,7 +20592,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>144</v>
       </c>
@@ -20634,7 +20637,7 @@
         <v>2.5412637704730561E-5</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>146</v>
       </c>
@@ -20679,7 +20682,7 @@
         <v>1.270631885236528E-5</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>150</v>
       </c>
@@ -20724,7 +20727,7 @@
         <v>2.5412637704730561E-5</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>158</v>
       </c>
@@ -20769,7 +20772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>162</v>
       </c>
@@ -20814,7 +20817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -20859,7 +20862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>171</v>
       </c>
@@ -20904,7 +20907,7 @@
         <v>1.1003672126148334E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>173</v>
       </c>
@@ -20949,7 +20952,7 @@
         <v>7.6237913114191687E-4</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="14.5">
+    <row r="87" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
         <v>177</v>
       </c>
@@ -20994,7 +20997,7 @@
         <v>1.1829582851552077E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="18.5">
+    <row r="90" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A90" s="43" t="s">
         <v>64</v>
       </c>
@@ -21003,7 +21006,7 @@
         <v>21831.587082756254</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="18.5">
+    <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A91" s="43" t="s">
         <v>179</v>
       </c>
@@ -21012,12 +21015,12 @@
         <v>20290.14478354996</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="44" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D95" s="37"/>
       <c r="E95" s="37"/>
       <c r="F95" s="37"/>
@@ -21027,7 +21030,7 @@
       <c r="J95" s="37"/>
       <c r="K95" s="37"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B96" s="37"/>
       <c r="C96" s="37"/>
       <c r="D96" s="37"/>

--- a/SubRES_TMPL/SubRES_TRA_NewVehicles.xlsx
+++ b/SubRES_TMPL/SubRES_TRA_NewVehicles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DB867A-3B71-470A-99F5-9E94C8798621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6361C5-8AAF-4FD4-B5AD-D3A7E1FA45D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12643,18 +12643,14 @@
         <v>397.21899999999999</v>
       </c>
       <c r="J147" s="46">
-        <f t="shared" si="11"/>
-        <v>323.60950000000003</v>
+        <v>167.643</v>
       </c>
       <c r="K147" s="46">
-        <v>250</v>
-      </c>
-      <c r="L147" s="46">
-        <f t="shared" si="12"/>
-        <v>220</v>
-      </c>
+        <v>141.95599999999999</v>
+      </c>
+      <c r="L147" s="46"/>
       <c r="M147" s="46">
-        <v>130</v>
+        <v>113.565</v>
       </c>
       <c r="N147" s="46">
         <f>+N144*0.8</f>
